--- a/artfynd/A 10406-2025 artfynd.xlsx
+++ b/artfynd/A 10406-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>191686</v>
+        <v>107413920</v>
       </c>
       <c r="B2" t="n">
-        <v>73548</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78739</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1114</v>
+        <v>218</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelekslav</t>
+          <t>Ekspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lecanographa amylacea</t>
+          <t>Calicium quercinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ehrh. ex Pers.) Egea &amp; Torrente</t>
+          <t>Pers.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>100 m V Gäddnäs (08F1f10), Ög</t>
+          <t>100 m V Gäddnäs, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>524098.8914381232</v>
+        <v>524099</v>
       </c>
       <c r="R2" t="n">
-        <v>6456565.771079332</v>
+        <v>6456566</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -745,27 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2000-07-12</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-09-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2000-07-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>080515101 / BUE VIOL / Enstaka-sparsam (1)  / OBJ.AREA:0,2 ha</t>
+          <t>2011-09-16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,82 +757,72 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Grova ädellövträd /</t>
-        </is>
-      </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Gammal grov ek</t>
+          <t>Gammal ek (GAMMALEK)</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Niklas Lönnell</t>
+          <t>Anders Engström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jens Johannesson</t>
+          <t>Via Anders Engström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>101489635</v>
+        <v>209514</v>
       </c>
       <c r="B3" t="n">
-        <v>106964</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>83304</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220299</v>
+        <v>311</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Brun nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Chaenotheca phaeocephala</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Turner) Th.Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gröndal, Gammalkil, Linköpings kommun, Ög</t>
+          <t>100 m NV Gäddnäs (08F1f09), Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>524122.6640714804</v>
+        <v>524124</v>
       </c>
       <c r="R3" t="n">
-        <v>6456558.547528731</v>
+        <v>6456642</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,22 +846,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-06-07</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2000-07-12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-06-07</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2000-07-12</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>080515091 / CHA PHAE / Tämligen allmän (2)  / OBJ.AREA:0,1 ha</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,53 +867,62 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Grova ädellövträd /</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Gammal grov ek</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Felicia Skorsdal</t>
+          <t>Niklas Lönnell</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Felicia Skorsdal</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Jens Johannesson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>101489652</v>
+        <v>101489656</v>
       </c>
       <c r="B4" t="n">
-        <v>77956</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83304</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>374</v>
+        <v>311</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gul dropplav</t>
+          <t>Brun nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cliostomum corrugatum</t>
+          <t>Chaenotheca phaeocephala</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.:Fr.) Fr.</t>
+          <t>(Turner) Th.Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -958,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>524113.2531988956</v>
+        <v>524244</v>
       </c>
       <c r="R4" t="n">
-        <v>6456545.33210774</v>
+        <v>6456655</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -991,19 +965,9 @@
           <t>2022-06-07</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-06-07</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,53 +998,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>101489653</v>
+        <v>107413918</v>
       </c>
       <c r="B5" t="n">
-        <v>77956</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83304</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>374</v>
+        <v>311</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gul dropplav</t>
+          <t>Brun nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cliostomum corrugatum</t>
+          <t>Chaenotheca phaeocephala</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.:Fr.) Fr.</t>
+          <t>(Turner) Th.Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gröndal, Gammalkil, Linköpings kommun, Ög</t>
+          <t>100 m V Gäddnäs, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>524198.4640134443</v>
+        <v>524099</v>
       </c>
       <c r="R5" t="n">
-        <v>6456580.06335375</v>
+        <v>6456566</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1104,22 +1063,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-06-07</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-09-16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-06-07</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-09-16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,73 +1079,73 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Gammal ek (GAMMALEK)</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Felicia Skorsdal</t>
+          <t>Anders Engström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Felicia Skorsdal</t>
+          <t>Via Anders Engström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>Linköpings kommuns naturvårdsprogram 2023</t>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>101489651</v>
+        <v>6741715</v>
       </c>
       <c r="B6" t="n">
-        <v>76907</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79795</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6436</v>
+        <v>374</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gulpudrad spiklav</t>
+          <t>Gul dropplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Calicium adspersum</t>
+          <t>Cliostomum corrugatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Pers.</t>
+          <t>(Ach.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gröndal, Gammalkil, Linköpings kommun, Ög</t>
+          <t>100 m V Gäddnäs (08F1f10), Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>524112.2307166659</v>
+        <v>524099</v>
       </c>
       <c r="R6" t="n">
-        <v>6456540.062649041</v>
+        <v>6456566</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1220,22 +1169,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-06-07</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2000-07-12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-06-07</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2000-07-12</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>080515101 / CLI CORR / Allmän-riklig (3)  / OBJ.AREA:0,2 ha</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1246,73 +1190,78 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Grova ädellövträd /</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Gammal grov ek</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Felicia Skorsdal</t>
+          <t>Niklas Lönnell</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Felicia Skorsdal</t>
+          <t>Jens Johannesson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>Linköpings kommuns naturvårdsprogram 2023</t>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>107413918</v>
+        <v>101489652</v>
       </c>
       <c r="B7" t="n">
-        <v>73690</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79795</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>311</v>
+        <v>374</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brun nållav</t>
+          <t>Gul dropplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca phaeocephala</t>
+          <t>Cliostomum corrugatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Turner) Th.Fr.</t>
+          <t>(Ach.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>100 m V Gäddnäs, Ög</t>
+          <t>Gröndal, Gammalkil, Linköpings kommun, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>524098.8914381232</v>
+        <v>524113</v>
       </c>
       <c r="R7" t="n">
-        <v>6456565.771079332</v>
+        <v>6456545</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1336,22 +1285,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2011-09-16</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2011-09-16</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-07</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,40 +1301,30 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Gammal ek (GAMMALEK)</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Engström</t>
+          <t>Felicia Skorsdal</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Via Anders Engström</t>
+          <t>Felicia Skorsdal</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
+          <t>Linköpings kommuns naturvårdsprogram 2023</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>107413919</v>
+        <v>101489653</v>
       </c>
       <c r="B8" t="n">
-        <v>88270</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79795</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1403,37 +1332,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>655</v>
+        <v>374</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Oxtungssvamp</t>
+          <t>Gul dropplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fistulina hepatica</t>
+          <t>Cliostomum corrugatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schaeff.) With., nom sanct.</t>
+          <t>(Ach.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>100 m V Gäddnäs, Ög</t>
+          <t>Gröndal, Gammalkil, Linköpings kommun, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>524098.8914381232</v>
+        <v>524199</v>
       </c>
       <c r="R8" t="n">
-        <v>6456565.771079332</v>
+        <v>6456580</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1457,22 +1386,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2011-09-16</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2011-09-16</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1483,62 +1402,52 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Gammal ek (GAMMALEK)</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Engström</t>
+          <t>Felicia Skorsdal</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Via Anders Engström</t>
+          <t>Felicia Skorsdal</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
+          <t>Linköpings kommuns naturvårdsprogram 2023</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>107413920</v>
+        <v>107413919</v>
       </c>
       <c r="B9" t="n">
-        <v>76919</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90801</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>218</v>
+        <v>655</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ekspik</t>
+          <t>Oxtungssvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Calicium quercinum</t>
+          <t>Fistulina hepatica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Pers.</t>
+          <t>(Schaeff.) With., nom sanct.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1548,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>524098.8914381232</v>
+        <v>524099</v>
       </c>
       <c r="R9" t="n">
-        <v>6456565.771079332</v>
+        <v>6456566</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1581,19 +1490,9 @@
           <t>2011-09-16</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2011-09-16</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1624,6 +1523,431 @@
       <c r="AY9" t="inlineStr">
         <is>
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>191686</v>
+      </c>
+      <c r="B10" t="n">
+        <v>75341</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1114</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Gammelekslav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lecanographa amylacea</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ehrh. ex Pers.) Egea &amp; Torrente</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>100 m V Gäddnäs (08F1f10), Ög</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>524099</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6456566</v>
+      </c>
+      <c r="S10" t="n">
+        <v>50</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Gammalkil</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2000-07-12</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2000-07-12</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>080515101 / BUE VIOL / Enstaka-sparsam (1)  / OBJ.AREA:0,2 ha</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Grova ädellövträd /</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Gammal grov ek</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Jens Johannesson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>101489651</v>
+      </c>
+      <c r="B11" t="n">
+        <v>78728</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6436</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Gulpudrad spiklav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Calicium adspersum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Pers.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Gröndal, Gammalkil, Linköpings kommun, Ög</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>524112</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6456540</v>
+      </c>
+      <c r="S11" t="n">
+        <v>15</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Gammalkil</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2022-06-07</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2022-06-07</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Felicia Skorsdal</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Felicia Skorsdal</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Linköpings kommuns naturvårdsprogram 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>101489635</v>
+      </c>
+      <c r="B12" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Gröndal, Gammalkil, Linköpings kommun, Ög</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>524123</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6456558</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Gammalkil</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2022-06-07</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2022-06-07</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Felicia Skorsdal</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Felicia Skorsdal</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>4920103</v>
+      </c>
+      <c r="B13" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>100 m V Gäddnäs (08F1f10), Ög</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>524099</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6456566</v>
+      </c>
+      <c r="S13" t="n">
+        <v>50</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Gammalkil</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2000-07-12</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2000-07-12</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>080515101 / DAPH MEZ / Enstaka-sparsam (1)  / OBJ.AREA:0,2 ha</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Grova ädellövträd /</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Jens Johannesson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 10406-2025 artfynd.xlsx
+++ b/artfynd/A 10406-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107413920</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/209514</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -995,6 +1010,11 @@
           <t>Linköpings kommuns naturvårdsprogram 2023</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101489656</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1101,6 +1121,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107413918</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1217,6 +1242,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6741715</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1318,6 +1348,11 @@
           <t>Linköpings kommuns naturvårdsprogram 2023</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101489652</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1419,6 +1454,11 @@
           <t>Linköpings kommuns naturvårdsprogram 2023</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101489653</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1525,6 +1565,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107413919</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1641,6 +1686,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/191686</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1742,6 +1792,11 @@
           <t>Linköpings kommuns naturvårdsprogram 2023</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101489651</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1839,6 +1894,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101489635</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1950,8 +2010,27 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4920103</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>